--- a/ig/DM-MARS-2026/ValueSet-jdv-registre-ern-cisis.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-jdv-registre-ern-cisis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="83">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142104</t>
+    <t>20260311144903</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:04+01:00</t>
+    <t>2026-03-11T14:49:03+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -240,13 +240,19 @@
     <t>GEN-373</t>
   </si>
   <si>
-    <t>Le patient a signé son consentement à la transmission des données au registre Endo-ERN EuRREB</t>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN Endo-ERN EuRREB</t>
   </si>
   <si>
     <t>GEN-416</t>
   </si>
   <si>
-    <t>Le patient a signé un consentement à la transmission de ses données au registre EuRREB</t>
+    <t>Le patient a signé son consentement à la transmission des données au registre ENR EuRREB</t>
+  </si>
+  <si>
+    <t>GEN-422</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN GloBE-Reg</t>
   </si>
   <si>
     <t/>
@@ -519,7 +525,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -739,15 +745,23 @@
         <v>78</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>80</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-MARS-2026/ValueSet-jdv-registre-ern-cisis.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-jdv-registre-ern-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144903</t>
+    <t>20260420150250</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:03+01:00</t>
+    <t>2026-04-20T15:02:50+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
